--- a/scenarios/Coal_Flexibilisation/sub_scenarios/weather.xlsx
+++ b/scenarios/Coal_Flexibilisation/sub_scenarios/weather.xlsx
@@ -1,45 +1,68 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rlinstitutde-my.sharepoint.com/personal/agatha_majcher_rl-institut_de/Documents/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_BB4A23EE9451101F6C1870945440D6BD9E17020D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2982C1C-1721-4873-888C-8A1274B0E27C}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1170" yWindow="735" windowWidth="17880" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="weather_years" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="weather_years" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>W_P50</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,102 +70,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,285 +358,182 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AK3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="20.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="5" bestFit="1" customWidth="1" min="2" max="37"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="27" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
         <v>2025</v>
       </c>
       <c r="C1">
-        <f>B1+1</f>
-        <v/>
+        <v>2026</v>
       </c>
       <c r="D1">
-        <f>C1+1</f>
-        <v/>
+        <v>2027</v>
       </c>
       <c r="E1">
-        <f>D1+1</f>
-        <v/>
+        <v>2028</v>
       </c>
       <c r="F1">
-        <f>E1+1</f>
-        <v/>
+        <v>2029</v>
       </c>
       <c r="G1">
-        <f>F1+1</f>
-        <v/>
+        <v>2030</v>
       </c>
       <c r="H1">
-        <f>G1+1</f>
-        <v/>
+        <v>2031</v>
       </c>
       <c r="I1">
-        <f>H1+1</f>
-        <v/>
+        <v>2032</v>
       </c>
       <c r="J1">
-        <f>I1+1</f>
-        <v/>
+        <v>2033</v>
       </c>
       <c r="K1">
-        <f>J1+1</f>
-        <v/>
+        <v>2034</v>
       </c>
       <c r="L1">
-        <f>K1+1</f>
-        <v/>
+        <v>2035</v>
       </c>
       <c r="M1">
-        <f>L1+1</f>
-        <v/>
+        <v>2036</v>
       </c>
       <c r="N1">
-        <f>M1+1</f>
-        <v/>
+        <v>2037</v>
       </c>
       <c r="O1">
-        <f>N1+1</f>
-        <v/>
+        <v>2038</v>
       </c>
       <c r="P1">
-        <f>O1+1</f>
-        <v/>
+        <v>2039</v>
       </c>
       <c r="Q1">
-        <f>P1+1</f>
-        <v/>
+        <v>2040</v>
       </c>
       <c r="R1">
-        <f>Q1+1</f>
-        <v/>
+        <v>2041</v>
       </c>
       <c r="S1">
-        <f>R1+1</f>
-        <v/>
+        <v>2042</v>
       </c>
       <c r="T1">
-        <f>S1+1</f>
-        <v/>
+        <v>2043</v>
       </c>
       <c r="U1">
-        <f>T1+1</f>
-        <v/>
+        <v>2044</v>
       </c>
       <c r="V1">
-        <f>U1+1</f>
-        <v/>
+        <v>2045</v>
       </c>
       <c r="W1">
-        <f>V1+1</f>
-        <v/>
+        <v>2046</v>
       </c>
       <c r="X1">
-        <f>W1+1</f>
-        <v/>
+        <v>2047</v>
       </c>
       <c r="Y1">
-        <f>X1+1</f>
-        <v/>
+        <v>2048</v>
       </c>
       <c r="Z1">
-        <f>Y1+1</f>
-        <v/>
+        <v>2049</v>
       </c>
       <c r="AA1">
-        <f>Z1+1</f>
-        <v/>
-      </c>
-      <c r="AB1">
-        <f>AA1+1</f>
-        <v/>
-      </c>
-      <c r="AC1">
-        <f>AB1+1</f>
-        <v/>
-      </c>
-      <c r="AD1">
-        <f>AC1+1</f>
-        <v/>
-      </c>
-      <c r="AE1">
-        <f>AD1+1</f>
-        <v/>
-      </c>
-      <c r="AF1">
-        <f>AE1+1</f>
-        <v/>
-      </c>
-      <c r="AG1">
-        <f>AF1+1</f>
-        <v/>
-      </c>
-      <c r="AH1">
-        <f>AG1+1</f>
-        <v/>
-      </c>
-      <c r="AI1">
-        <f>AH1+1</f>
-        <v/>
-      </c>
-      <c r="AJ1">
-        <f>AI1+1</f>
-        <v/>
-      </c>
-      <c r="AK1">
-        <f>AJ1+1</f>
-        <v/>
+        <v>2050</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>W_P50</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="AK2" t="n">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2018</v>
+      </c>
+      <c r="C2">
+        <v>2018</v>
+      </c>
+      <c r="D2">
+        <v>2018</v>
+      </c>
+      <c r="E2">
+        <v>2018</v>
+      </c>
+      <c r="F2">
+        <v>2018</v>
+      </c>
+      <c r="G2">
+        <v>2018</v>
+      </c>
+      <c r="H2">
+        <v>2018</v>
+      </c>
+      <c r="I2">
+        <v>2018</v>
+      </c>
+      <c r="J2">
+        <v>2018</v>
+      </c>
+      <c r="K2">
+        <v>2018</v>
+      </c>
+      <c r="L2">
+        <v>2018</v>
+      </c>
+      <c r="M2">
+        <v>2018</v>
+      </c>
+      <c r="N2">
+        <v>2018</v>
+      </c>
+      <c r="O2">
+        <v>2018</v>
+      </c>
+      <c r="P2">
+        <v>2018</v>
+      </c>
+      <c r="Q2">
+        <v>2018</v>
+      </c>
+      <c r="R2">
+        <v>2018</v>
+      </c>
+      <c r="S2">
+        <v>2018</v>
+      </c>
+      <c r="T2">
+        <v>2018</v>
+      </c>
+      <c r="U2">
+        <v>2018</v>
+      </c>
+      <c r="V2">
+        <v>2018</v>
+      </c>
+      <c r="W2">
+        <v>2018</v>
+      </c>
+      <c r="X2">
+        <v>2018</v>
+      </c>
+      <c r="Y2">
+        <v>2018</v>
+      </c>
+      <c r="Z2">
+        <v>2018</v>
+      </c>
+      <c r="AA2">
         <v>2018</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n"/>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
